--- a/ACCY122/Session/S09/ACCY122 In Session L9 v2.0.xlsx
+++ b/ACCY122/Session/S09/ACCY122 In Session L9 v2.0.xlsx
@@ -1,27 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onlym\Desktop\Manek\Notes\SIM\UOW\2025 UOW\Learning Material\In Session Explanation\2025\L9\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Session\S09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECBA5B0-5438-4F25-A117-F8FD6CE5D1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA7D765-2AD8-4657-A3F2-A5414A0FFC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" activeTab="4" xr2:uid="{BB81D00E-B7BD-4C7E-833A-F8ECA5DA9AD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{BB81D00E-B7BD-4C7E-833A-F8ECA5DA9AD9}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="7" r:id="rId1"/>
     <sheet name="System (2)" sheetId="8" r:id="rId2"/>
     <sheet name="NCA Explain" sheetId="14" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="15" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="16" r:id="rId5"/>
-    <sheet name="NCA Explain (2)" sheetId="17" r:id="rId6"/>
+    <sheet name="NCA Explain (2)" sheetId="17" r:id="rId4"/>
+    <sheet name="14.1 A" sheetId="22" r:id="rId5"/>
+    <sheet name="14.3 A" sheetId="23" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="16" r:id="rId7"/>
+    <sheet name="Sheet3" sheetId="18" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="15" r:id="rId9"/>
+    <sheet name="Sheet4" sheetId="19" r:id="rId10"/>
+    <sheet name="Sheet5" sheetId="20" r:id="rId11"/>
+    <sheet name="Sheet6" sheetId="21" r:id="rId12"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <definedNames>
     <definedName name="BLPH1" hidden="1">'[1]Template (XFA)'!#REF!</definedName>
@@ -118,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="279">
   <si>
     <t>Transactions</t>
   </si>
@@ -772,18 +778,6 @@
     <t>Equipment</t>
   </si>
   <si>
-    <t>LBE</t>
-  </si>
-  <si>
-    <t>Legal fees</t>
-  </si>
-  <si>
-    <t>Commission</t>
-  </si>
-  <si>
-    <t>Appraisal</t>
-  </si>
-  <si>
     <t>d</t>
   </si>
   <si>
@@ -824,6 +818,234 @@
   </si>
   <si>
     <t>U of P method</t>
+  </si>
+  <si>
+    <t>a)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LBE </t>
+  </si>
+  <si>
+    <t>Legal Fees</t>
+  </si>
+  <si>
+    <t>Commissions</t>
+  </si>
+  <si>
+    <t>Appraisal Fee</t>
+  </si>
+  <si>
+    <t>b)</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freight </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Oil lubricants and supplies are ongoing operating expenses - used during operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Insurance are occuring operating expense </t>
+  </si>
+  <si>
+    <t>1 / 8 = 12.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight Line </t>
+  </si>
+  <si>
+    <t>(40k - 4k) / 4 = 9k</t>
+  </si>
+  <si>
+    <t>Units of activity</t>
+  </si>
+  <si>
+    <t>40k - 4k = 36k</t>
+  </si>
+  <si>
+    <t>36k/100k = 0.36</t>
+  </si>
+  <si>
+    <t>0.36 x 27.5k = 9900</t>
+  </si>
+  <si>
+    <t>Diminishing bal method</t>
+  </si>
+  <si>
+    <t>year 1 = 40k - (40k x 25%) = 30k</t>
+  </si>
+  <si>
+    <t>year 2 = (30k x 25%) = 7.5k</t>
+  </si>
+  <si>
+    <t>(60k-5k)/5 = 11k</t>
+  </si>
+  <si>
+    <t>11k dep per year</t>
+  </si>
+  <si>
+    <t>(60k-5k)/100k units = 0.55</t>
+  </si>
+  <si>
+    <t>0.55 per unit</t>
+  </si>
+  <si>
+    <t>16k x 0.55=8.8k</t>
+  </si>
+  <si>
+    <t>24k x 0.55=13.2k</t>
+  </si>
+  <si>
+    <t>22k</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation</t>
+  </si>
+  <si>
+    <t>60k - 22k = 38k</t>
+  </si>
+  <si>
+    <t>Book value</t>
+  </si>
+  <si>
+    <t>(400k-30k) / 10 = 37k</t>
+  </si>
+  <si>
+    <t>(37k/12) x 3 = 9.25k</t>
+  </si>
+  <si>
+    <t>year 1 = 9.25k</t>
+  </si>
+  <si>
+    <t>year 2 = 37k</t>
+  </si>
+  <si>
+    <t>double declining means reducing bal method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">so double declining means x 2 </t>
+  </si>
+  <si>
+    <t>dep rate = 10% x 2 = 20%</t>
+  </si>
+  <si>
+    <t>400k x 20% = 80k</t>
+  </si>
+  <si>
+    <t>(80k/12) x 3 = 20k</t>
+  </si>
+  <si>
+    <t>(400k - 20k) x 20% = 76k</t>
+  </si>
+  <si>
+    <t>year 1 = 20k</t>
+  </si>
+  <si>
+    <t>year 2 = 76k</t>
+  </si>
+  <si>
+    <t>c)</t>
+  </si>
+  <si>
+    <t>dr ($)</t>
+  </si>
+  <si>
+    <t>cr ($)</t>
+  </si>
+  <si>
+    <t>Loan (long term)</t>
+  </si>
+  <si>
+    <t>(Purchase NCA in cash and credit)</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
+  <si>
+    <t>32.4k - 6 = 26.4k</t>
+  </si>
+  <si>
+    <t>26.4k / 4 = 6.6k</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>dep exp</t>
+  </si>
+  <si>
+    <t>6.6k</t>
+  </si>
+  <si>
+    <t>accum dep</t>
+  </si>
+  <si>
+    <t>13.2k</t>
+  </si>
+  <si>
+    <t>19.8k</t>
+  </si>
+  <si>
+    <t>26.4k</t>
+  </si>
+  <si>
+    <t>net book value</t>
+  </si>
+  <si>
+    <t>25.8k</t>
+  </si>
+  <si>
+    <t>32.4k</t>
+  </si>
+  <si>
+    <t>19.2k</t>
+  </si>
+  <si>
+    <t>12.6k</t>
+  </si>
+  <si>
+    <t>6k</t>
+  </si>
+  <si>
+    <t>d)</t>
+  </si>
+  <si>
+    <t>26.4k / 200k = 0.132</t>
+  </si>
+  <si>
+    <t>40k x 0.132 = 5.28k</t>
+  </si>
+  <si>
+    <t>45k x 0.132 = 5.94k</t>
+  </si>
+  <si>
+    <t>68k x 0.132 = 8.976k</t>
+  </si>
+  <si>
+    <t>47k x 0.132 = 6.204k</t>
+  </si>
+  <si>
+    <t>5.28k</t>
+  </si>
+  <si>
+    <t>11.2k</t>
+  </si>
+  <si>
+    <t>17.424k</t>
+  </si>
+  <si>
+    <t>27.12k</t>
+  </si>
+  <si>
+    <t>21.18k</t>
+  </si>
+  <si>
+    <t>14.976k</t>
   </si>
 </sst>
 </file>
@@ -831,9 +1053,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -886,13 +1108,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -960,7 +1184,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1131,10 +1355,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1191,17 +1426,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1215,32 +1450,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1287,8 +1526,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1023447" y="636641"/>
-          <a:ext cx="5361327" cy="5677194"/>
+          <a:off x="1026232" y="661707"/>
+          <a:ext cx="5386393" cy="5936207"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -1777,6 +2016,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>58085</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>143141</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{698A17FD-D35B-CC2A-D370-A0581D66E501}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676275" y="523875"/>
+          <a:ext cx="6697010" cy="1905266"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1836,6 +2130,713 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>141925</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>47911</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E2C75D9-EF3F-B087-54AB-D0A3EF42809F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="571500" y="285750"/>
+          <a:ext cx="6725589" cy="2048161"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>307731</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>58615</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>246582</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>153931</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45433BAD-0AF6-3A12-D464-CF77168F7D4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="915866" y="2344615"/>
+          <a:ext cx="5877745" cy="476316"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>256442</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>14654</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>73001</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>119577</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79BACF21-2904-7DD6-F647-DEA3AC582AF5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="864577" y="2872154"/>
+          <a:ext cx="6363588" cy="1057423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>222054</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C9D8E8E-E0FD-31E8-9D5F-2935F9EAF665}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="523875" y="200024"/>
+          <a:ext cx="7452186" cy="2200275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>562060</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>66714</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78A0C3FC-25A7-D00F-21AB-64B9774D1C18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="561975" y="2457450"/>
+          <a:ext cx="5315692" cy="276264"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>476240</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>44</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30DE74D5-82AB-32E5-E25C-76A1C010D735}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="542925" y="2733675"/>
+          <a:ext cx="4639322" cy="314369"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>181179</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95312</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{831E9657-B0C2-3E37-6A46-9775A2C191A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="542925" y="3076575"/>
+          <a:ext cx="6173061" cy="447737"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>132234</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>45</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB5FC50C-0230-69D4-B98C-0BB8F4B07D39}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="542925" y="3676650"/>
+          <a:ext cx="6125430" cy="323895"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>119743</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>591911</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11265" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0C917A0-C24C-6909-5F89-01007834C23E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="119743" y="285750"/>
+          <a:ext cx="7150554" cy="962025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>564173</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>168519</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>6045</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>64128</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27E2F0DD-7B94-46F0-2D83-690D5D61582E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="564173" y="168519"/>
+          <a:ext cx="6563641" cy="2753109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>697648</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10241" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FC9BBE0-C73B-89C2-683E-1DEF861414FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="19050"/>
+          <a:ext cx="4048125" cy="1438275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>513522</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>74544</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>439910</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>112995</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C796CFD1-7E22-EF59-CD8C-319FC8DC989C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="513522" y="265044"/>
+          <a:ext cx="6668431" cy="2514951"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>496239</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>28961</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC5402A1-CA18-C1C4-0B7F-2F97EB362F92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="476250" y="314325"/>
+          <a:ext cx="6725589" cy="2762636"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2189,8 +3190,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8D626B-C14C-46B5-8E1C-4CA9F7E39F10}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F15396-A262-46DD-B8D3-B72BB0D6B970}">
+  <dimension ref="B18:B28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>223</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA45396-D7BA-4C74-972A-47181BB92B9B}">
+  <dimension ref="B19:F29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C25">
+        <v>2018</v>
+      </c>
+      <c r="D25" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C26">
+        <v>2019</v>
+      </c>
+      <c r="D26" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E27" s="77" t="s">
+        <v>230</v>
+      </c>
+      <c r="F27" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>232</v>
+      </c>
+      <c r="F29" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4422671-5A9A-4CF2-B9AE-F96D3B78ADF6}">
+  <dimension ref="B17:C34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>245</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2199,27 +3403,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C8C239-724E-42F6-AF35-C0937B854444}">
   <dimension ref="B1:O20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
         <v>7</v>
       </c>
@@ -2236,7 +3440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="10" t="s">
         <v>11</v>
       </c>
@@ -2254,7 +3458,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="11" t="s">
@@ -2268,8 +3472,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C6" s="71" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C6" s="73" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="10"/>
@@ -2296,8 +3500,8 @@
       </c>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C7" s="71"/>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C7" s="73"/>
       <c r="D7" s="10"/>
       <c r="E7" s="11" t="s">
         <v>2</v>
@@ -2309,8 +3513,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C8" s="71"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C8" s="73"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
         <v>22</v>
@@ -2323,8 +3527,8 @@
       </c>
       <c r="O8" s="6"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C9" s="71"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C9" s="73"/>
       <c r="D9" s="10"/>
       <c r="E9" s="11" t="s">
         <v>2</v>
@@ -2332,8 +3536,8 @@
       <c r="M9" s="5"/>
       <c r="O9" s="6"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C10" s="71"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C10" s="73"/>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
         <v>24</v>
@@ -2361,7 +3565,7 @@
       </c>
       <c r="O10" s="6"/>
     </row>
-    <row r="11" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -2381,7 +3585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
       <c r="E12" s="11" t="s">
@@ -2398,7 +3602,7 @@
       </c>
       <c r="O12" s="6"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C13" s="10" t="s">
         <v>34</v>
       </c>
@@ -2415,7 +3619,7 @@
       <c r="M13" s="5"/>
       <c r="O13" s="6"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
         <v>36</v>
       </c>
@@ -2433,7 +3637,7 @@
       </c>
       <c r="O14" s="6"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M15" s="5" t="s">
         <v>38</v>
       </c>
@@ -2441,17 +3645,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M16" s="5" t="s">
         <v>39</v>
       </c>
       <c r="O16" s="6"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M17" s="5"/>
       <c r="O17" s="6"/>
     </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K18">
         <v>4</v>
       </c>
@@ -2466,7 +3670,7 @@
       </c>
       <c r="O18" s="6"/>
     </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M19" s="5" t="s">
         <v>42</v>
       </c>
@@ -2474,7 +3678,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="11:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M20" s="7" t="s">
         <v>43</v>
       </c>
@@ -2495,27 +3699,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C192E2A4-4D11-49C6-ABB6-8EC084802FB4}">
   <dimension ref="A1:W115"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.1796875" customWidth="1"/>
-    <col min="3" max="3" width="50.36328125" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="50.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="23.08984375" customWidth="1"/>
-    <col min="9" max="9" width="13.54296875" customWidth="1"/>
-    <col min="10" max="10" width="8.7265625" customWidth="1"/>
-    <col min="11" max="11" width="9.6328125" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" customWidth="1"/>
-    <col min="14" max="14" width="15.54296875" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D1" s="15"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J2" t="s">
         <v>44</v>
       </c>
@@ -2532,7 +3736,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -2540,12 +3744,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -2553,22 +3757,22 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9" s="16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>56</v>
       </c>
@@ -2576,7 +3780,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>58</v>
       </c>
@@ -2584,12 +3788,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
         <v>61</v>
       </c>
@@ -2597,7 +3801,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B23" s="16" t="s">
         <v>63</v>
       </c>
@@ -2611,7 +3815,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>67</v>
       </c>
@@ -2625,7 +3829,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E25" s="16" t="s">
         <v>71</v>
       </c>
@@ -2633,7 +3837,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -2642,12 +3846,12 @@
       <c r="F26" s="17"/>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B27" s="18" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="19" t="s">
         <v>73</v>
       </c>
@@ -2667,7 +3871,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D29" s="2"/>
       <c r="E29" s="21" t="s">
         <v>77</v>
@@ -2682,7 +3886,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D30" s="5" t="s">
         <v>79</v>
       </c>
@@ -2696,7 +3900,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D31" s="5" t="s">
         <v>80</v>
       </c>
@@ -2710,7 +3914,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D32" s="5" t="s">
         <v>81</v>
       </c>
@@ -2726,7 +3930,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D33" s="5" t="s">
         <v>82</v>
       </c>
@@ -2742,7 +3946,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="34" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D34" s="7" t="s">
         <v>73</v>
       </c>
@@ -2751,16 +3955,16 @@
         <v>43000</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E35" s="25"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>83</v>
       </c>
       <c r="E36" s="25"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>1</v>
       </c>
@@ -2769,7 +3973,7 @@
       </c>
       <c r="E37" s="25"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>2</v>
       </c>
@@ -2780,12 +3984,12 @@
         <v>365</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J39">
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>86</v>
       </c>
@@ -2797,7 +4001,7 @@
         <v>8760</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>87</v>
       </c>
@@ -2809,7 +4013,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>89</v>
       </c>
@@ -2820,7 +4024,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
         <v>91</v>
       </c>
@@ -2835,7 +4039,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>94</v>
       </c>
@@ -2843,7 +4047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>95</v>
       </c>
@@ -2860,12 +4064,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G46" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>100</v>
       </c>
@@ -2873,12 +4077,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="10" t="s">
         <v>103</v>
       </c>
@@ -2889,7 +4093,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="16" t="s">
         <v>106</v>
       </c>
@@ -2900,7 +4104,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>1</v>
       </c>
@@ -2914,7 +4118,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>2</v>
       </c>
@@ -2931,7 +4135,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>3</v>
       </c>
@@ -2946,7 +4150,7 @@
       </c>
       <c r="G55" s="28"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>4</v>
       </c>
@@ -2966,12 +4170,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="58" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I58" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C59" s="2"/>
       <c r="D59" s="3" t="s">
         <v>123</v>
@@ -2993,7 +4197,7 @@
       <c r="K59" s="3"/>
       <c r="L59" s="4"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C60" s="5" t="s">
         <v>128</v>
       </c>
@@ -3020,7 +4224,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C61" s="5">
         <v>1</v>
       </c>
@@ -3054,7 +4258,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C62" s="5">
         <v>2</v>
       </c>
@@ -3088,7 +4292,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C63" s="5">
         <v>3</v>
       </c>
@@ -3122,7 +4326,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C64" s="5">
         <v>4</v>
       </c>
@@ -3156,7 +4360,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="65" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C65" s="5">
         <v>4</v>
       </c>
@@ -3180,7 +4384,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="66" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C66" s="7" t="s">
         <v>131</v>
       </c>
@@ -3209,7 +4413,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>1</v>
       </c>
@@ -3217,7 +4421,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C69" t="s">
         <v>140</v>
       </c>
@@ -3228,7 +4432,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>142</v>
       </c>
@@ -3236,8 +4440,8 @@
         <v>143</v>
       </c>
     </row>
-    <row r="71" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="72" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C72" s="2" t="s">
         <v>112</v>
       </c>
@@ -3266,7 +4470,7 @@
       <c r="V72" s="3"/>
       <c r="W72" s="4"/>
     </row>
-    <row r="73" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C73" s="5"/>
       <c r="D73" t="s">
         <v>128</v>
@@ -3296,7 +4500,7 @@
       </c>
       <c r="W73" s="6"/>
     </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C74" s="42"/>
       <c r="D74" s="30" t="s">
         <v>73</v>
@@ -3344,7 +4548,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>147</v>
       </c>
@@ -3407,7 +4611,7 @@
         <v>3024.8049268750005</v>
       </c>
     </row>
-    <row r="76" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>151</v>
       </c>
@@ -3463,7 +4667,7 @@
       </c>
       <c r="W76" s="6"/>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>147</v>
       </c>
@@ -3505,7 +4709,7 @@
       </c>
       <c r="W77" s="6"/>
     </row>
-    <row r="78" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>151</v>
       </c>
@@ -3537,7 +4741,7 @@
         <v>2999.8049268750005</v>
       </c>
     </row>
-    <row r="79" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>147</v>
       </c>
@@ -3572,7 +4776,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>151</v>
       </c>
@@ -3589,7 +4793,7 @@
       </c>
       <c r="G80" s="41"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>147</v>
       </c>
@@ -3609,7 +4813,7 @@
         <v>40000.195073125004</v>
       </c>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>147</v>
       </c>
@@ -3623,7 +4827,7 @@
       </c>
       <c r="G82" s="56"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>151</v>
       </c>
@@ -3640,7 +4844,7 @@
       </c>
       <c r="G83" s="56"/>
     </row>
-    <row r="84" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C84" s="7" t="s">
         <v>89</v>
       </c>
@@ -3651,10 +4855,10 @@
       </c>
       <c r="G84" s="59"/>
     </row>
-    <row r="85" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F85" s="25"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
         <v>116</v>
       </c>
@@ -3665,7 +4869,7 @@
       </c>
       <c r="G86" s="4"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C87" s="5"/>
       <c r="D87" t="s">
         <v>128</v>
@@ -3678,7 +4882,7 @@
       </c>
       <c r="G87" s="6"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C88" s="5"/>
       <c r="D88">
         <v>1</v>
@@ -3693,7 +4897,7 @@
       <c r="G88" s="6"/>
       <c r="J88" s="62"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C89" s="5"/>
       <c r="D89">
         <v>2</v>
@@ -3708,7 +4912,7 @@
       <c r="G89" s="6"/>
       <c r="J89" s="62"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C90" s="5"/>
       <c r="D90">
         <v>3</v>
@@ -3723,7 +4927,7 @@
       <c r="G90" s="6"/>
       <c r="J90" s="62"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C91" s="5"/>
       <c r="D91">
         <v>4</v>
@@ -3737,7 +4941,7 @@
       </c>
       <c r="G91" s="6"/>
     </row>
-    <row r="92" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C92" s="63" t="s">
         <v>131</v>
       </c>
@@ -3751,8 +4955,8 @@
       </c>
       <c r="G92" s="9"/>
     </row>
-    <row r="94" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C95" t="s">
         <v>119</v>
       </c>
@@ -3765,7 +4969,7 @@
       </c>
       <c r="G95" s="21"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C96" s="5"/>
       <c r="D96" t="s">
         <v>128</v>
@@ -3778,7 +4982,7 @@
       </c>
       <c r="G96" s="65"/>
     </row>
-    <row r="97" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C97" s="5"/>
       <c r="D97">
         <v>1</v>
@@ -3792,7 +4996,7 @@
       </c>
       <c r="G97" s="6"/>
     </row>
-    <row r="98" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C98" s="5"/>
       <c r="D98">
         <v>2</v>
@@ -3806,7 +5010,7 @@
       </c>
       <c r="G98" s="6"/>
     </row>
-    <row r="99" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C99" s="5"/>
       <c r="D99">
         <v>3</v>
@@ -3820,7 +5024,7 @@
       </c>
       <c r="G99" s="6"/>
     </row>
-    <row r="100" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C100" s="5"/>
       <c r="D100">
         <v>4</v>
@@ -3834,7 +5038,7 @@
       </c>
       <c r="G100" s="6"/>
     </row>
-    <row r="101" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C101" s="63" t="s">
         <v>131</v>
       </c>
@@ -3848,8 +5052,8 @@
       </c>
       <c r="G101" s="9"/>
     </row>
-    <row r="103" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="104" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>103</v>
       </c>
@@ -3865,7 +5069,7 @@
       </c>
       <c r="H104" s="4"/>
     </row>
-    <row r="105" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C105" s="69" t="s">
         <v>171</v>
       </c>
@@ -3879,7 +5083,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="106" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C106" s="69" t="s">
         <v>173</v>
       </c>
@@ -3891,7 +5095,7 @@
       </c>
       <c r="H106" s="6"/>
     </row>
-    <row r="107" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C107" s="70" t="s">
         <v>176</v>
       </c>
@@ -3900,8 +5104,8 @@
       <c r="G107" s="8"/>
       <c r="H107" s="9"/>
     </row>
-    <row r="108" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="109" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="2:14" x14ac:dyDescent="0.25">
       <c r="I109" s="2" t="s">
         <v>75</v>
       </c>
@@ -3913,7 +5117,7 @@
       <c r="M109" s="3"/>
       <c r="N109" s="4"/>
     </row>
-    <row r="110" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D110">
         <v>1</v>
       </c>
@@ -3937,7 +5141,7 @@
       </c>
       <c r="N110" s="6"/>
     </row>
-    <row r="111" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>178</v>
       </c>
@@ -3956,7 +5160,7 @@
       <c r="I111" s="5"/>
       <c r="N111" s="6"/>
     </row>
-    <row r="112" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C112" s="2" t="s">
         <v>179</v>
       </c>
@@ -3987,7 +5191,7 @@
       </c>
       <c r="N112" s="6"/>
     </row>
-    <row r="113" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C113" s="5" t="s">
         <v>180</v>
       </c>
@@ -4024,7 +5228,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="114" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C114" s="7" t="s">
         <v>182</v>
       </c>
@@ -4057,7 +5261,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="115" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E115" s="16" t="s">
         <v>184</v>
       </c>
@@ -4088,335 +5292,29 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8603A5-ECDA-4924-BA5E-9368E679B896}">
-  <dimension ref="A9:F14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C63B16D-6262-4BBD-B8F1-DFD03BF45EE1}">
+  <dimension ref="A1:W115"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="50.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="23.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F9" s="16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B10" s="73">
-        <v>0.5</v>
-      </c>
-      <c r="C10" s="74">
-        <f>C$13*B10</f>
-        <v>1075000</v>
-      </c>
-      <c r="E10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F10" s="34">
-        <v>2100000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B11" s="75">
-        <v>0.3</v>
-      </c>
-      <c r="C11" s="76">
-        <f t="shared" ref="C11:C12" si="0">C$13*B11</f>
-        <v>645000</v>
-      </c>
-      <c r="E11" t="s">
-        <v>190</v>
-      </c>
-      <c r="F11" s="34">
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B12" s="75">
-        <v>0.2</v>
-      </c>
-      <c r="C12" s="76">
-        <f t="shared" si="0"/>
-        <v>430000</v>
-      </c>
-      <c r="E12" t="s">
-        <v>191</v>
-      </c>
-      <c r="F12" s="34">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="7"/>
-      <c r="B13" s="77">
-        <f>SUM(B10:B12)</f>
-        <v>1</v>
-      </c>
-      <c r="C13" s="78">
-        <f>F14</f>
-        <v>2150000</v>
-      </c>
-      <c r="E13" t="s">
-        <v>192</v>
-      </c>
-      <c r="F13" s="34">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E14" t="s">
-        <v>131</v>
-      </c>
-      <c r="F14" s="72">
-        <f>SUM(F10:F13)</f>
-        <v>2150000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12591C51-F13F-4D16-B1CA-1C7B32F3D87B}">
-  <dimension ref="C9:F24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="5.1796875" customWidth="1"/>
-    <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="9" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="25">
-        <v>46400</v>
-      </c>
-      <c r="E10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11">
-        <v>6400</v>
-      </c>
-      <c r="E11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" s="26">
-        <f>D10-D11</f>
-        <v>40000</v>
-      </c>
-      <c r="E12" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="27">
-        <v>4</v>
-      </c>
-      <c r="E13" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="14" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C14" t="s">
-        <v>195</v>
-      </c>
-      <c r="D14" s="25">
-        <v>500000</v>
-      </c>
-      <c r="E14" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="15" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C15" t="s">
-        <v>196</v>
-      </c>
-      <c r="D15">
-        <f>D12/D13</f>
-        <v>10000</v>
-      </c>
-      <c r="E15" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C16" t="s">
-        <v>198</v>
-      </c>
-      <c r="D16" s="79">
-        <f>D12/D14</f>
-        <v>0.08</v>
-      </c>
-      <c r="E16" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C18" t="s">
-        <v>200</v>
-      </c>
-      <c r="D18" t="s">
-        <v>205</v>
-      </c>
-      <c r="E18" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="D19" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C20" t="s">
-        <v>201</v>
-      </c>
-      <c r="D20" s="34">
-        <v>10000</v>
-      </c>
-      <c r="E20">
-        <f>F20*D$16</f>
-        <v>8800</v>
-      </c>
-      <c r="F20">
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C21" t="s">
-        <v>202</v>
-      </c>
-      <c r="D21" s="34">
-        <v>10000</v>
-      </c>
-      <c r="E21">
-        <f t="shared" ref="E21:E23" si="0">F21*D$16</f>
-        <v>9200</v>
-      </c>
-      <c r="F21">
-        <v>115000</v>
-      </c>
-    </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C22" t="s">
-        <v>203</v>
-      </c>
-      <c r="D22" s="34">
-        <v>10000</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>10160</v>
-      </c>
-      <c r="F22">
-        <v>127000</v>
-      </c>
-    </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C23" t="s">
-        <v>204</v>
-      </c>
-      <c r="D23" s="34">
-        <v>10000</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="0"/>
-        <v>11840</v>
-      </c>
-      <c r="F23">
-        <v>148000</v>
-      </c>
-    </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C24" t="s">
-        <v>131</v>
-      </c>
-      <c r="D24" s="72">
-        <f>SUM(D20:D23)</f>
-        <v>40000</v>
-      </c>
-      <c r="E24">
-        <f>F24*D$16</f>
-        <v>40000</v>
-      </c>
-      <c r="F24">
-        <f>SUM(F20:F23)</f>
-        <v>500000</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C63B16D-6262-4BBD-B8F1-DFD03BF45EE1}">
-  <dimension ref="A1:W115"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.1796875" customWidth="1"/>
-    <col min="3" max="3" width="50.36328125" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" customWidth="1"/>
-    <col min="6" max="6" width="13.81640625" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="23.08984375" customWidth="1"/>
-    <col min="9" max="9" width="13.54296875" customWidth="1"/>
-    <col min="10" max="10" width="8.7265625" customWidth="1"/>
-    <col min="11" max="11" width="9.6328125" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" customWidth="1"/>
-    <col min="14" max="14" width="15.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D1" s="15"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J2" t="s">
         <v>44</v>
       </c>
@@ -4433,7 +5331,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -4441,12 +5339,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>52</v>
       </c>
@@ -4454,22 +5352,22 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9" s="16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>56</v>
       </c>
@@ -4477,7 +5375,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>58</v>
       </c>
@@ -4485,12 +5383,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
         <v>61</v>
       </c>
@@ -4498,7 +5396,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B23" s="16" t="s">
         <v>63</v>
       </c>
@@ -4512,7 +5410,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>67</v>
       </c>
@@ -4526,7 +5424,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E25" s="16" t="s">
         <v>71</v>
       </c>
@@ -4534,7 +5432,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -4543,12 +5441,12 @@
       <c r="F26" s="17"/>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="1:11" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B27" s="18" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="19" t="s">
         <v>73</v>
       </c>
@@ -4568,7 +5466,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D29" s="2"/>
       <c r="E29" s="21" t="s">
         <v>77</v>
@@ -4583,7 +5481,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D30" s="5" t="s">
         <v>79</v>
       </c>
@@ -4597,7 +5495,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D31" s="5" t="s">
         <v>80</v>
       </c>
@@ -4611,7 +5509,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D32" s="5" t="s">
         <v>81</v>
       </c>
@@ -4627,7 +5525,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D33" s="5" t="s">
         <v>82</v>
       </c>
@@ -4643,7 +5541,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="34" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D34" s="7" t="s">
         <v>73</v>
       </c>
@@ -4652,16 +5550,16 @@
         <v>43000</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E35" s="25"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>83</v>
       </c>
       <c r="E36" s="25"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>1</v>
       </c>
@@ -4670,7 +5568,7 @@
       </c>
       <c r="E37" s="25"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>2</v>
       </c>
@@ -4681,12 +5579,12 @@
         <v>365</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="J39">
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>86</v>
       </c>
@@ -4698,7 +5596,7 @@
         <v>8760</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>87</v>
       </c>
@@ -4710,7 +5608,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>89</v>
       </c>
@@ -4721,7 +5619,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
         <v>91</v>
       </c>
@@ -4736,7 +5634,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>94</v>
       </c>
@@ -4744,7 +5642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>95</v>
       </c>
@@ -4761,12 +5659,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G46" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>100</v>
       </c>
@@ -4774,12 +5672,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="10" t="s">
         <v>103</v>
       </c>
@@ -4790,7 +5688,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B52" s="16" t="s">
         <v>106</v>
       </c>
@@ -4801,7 +5699,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B53">
         <v>1</v>
       </c>
@@ -4815,7 +5713,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54">
         <v>2</v>
       </c>
@@ -4832,7 +5730,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B55">
         <v>3</v>
       </c>
@@ -4847,7 +5745,7 @@
       </c>
       <c r="G55" s="28"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B56">
         <v>4</v>
       </c>
@@ -4867,12 +5765,12 @@
         <v>98</v>
       </c>
     </row>
-    <row r="58" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I58" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C59" s="2"/>
       <c r="D59" s="3" t="s">
         <v>123</v>
@@ -4894,7 +5792,7 @@
       <c r="K59" s="3"/>
       <c r="L59" s="4"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C60" s="5" t="s">
         <v>128</v>
       </c>
@@ -4921,7 +5819,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C61" s="5">
         <v>1</v>
       </c>
@@ -4955,7 +5853,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C62" s="5">
         <v>2</v>
       </c>
@@ -4989,7 +5887,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C63" s="5">
         <v>3</v>
       </c>
@@ -5023,7 +5921,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C64" s="5">
         <v>4</v>
       </c>
@@ -5057,7 +5955,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="65" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C65" s="5">
         <v>4</v>
       </c>
@@ -5081,7 +5979,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="66" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C66" s="7" t="s">
         <v>131</v>
       </c>
@@ -5110,7 +6008,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B68">
         <v>1</v>
       </c>
@@ -5118,7 +6016,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C69" t="s">
         <v>140</v>
       </c>
@@ -5129,7 +6027,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>142</v>
       </c>
@@ -5137,8 +6035,8 @@
         <v>143</v>
       </c>
     </row>
-    <row r="71" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="72" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C72" s="2" t="s">
         <v>112</v>
       </c>
@@ -5167,7 +6065,7 @@
       <c r="V72" s="3"/>
       <c r="W72" s="4"/>
     </row>
-    <row r="73" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C73" s="5"/>
       <c r="D73" t="s">
         <v>128</v>
@@ -5197,7 +6095,7 @@
       </c>
       <c r="W73" s="6"/>
     </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:23" x14ac:dyDescent="0.25">
       <c r="C74" s="42"/>
       <c r="D74" s="30" t="s">
         <v>73</v>
@@ -5245,7 +6143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>147</v>
       </c>
@@ -5308,7 +6206,7 @@
         <v>3024.8049268750005</v>
       </c>
     </row>
-    <row r="76" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>151</v>
       </c>
@@ -5364,7 +6262,7 @@
       </c>
       <c r="W76" s="6"/>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
         <v>147</v>
       </c>
@@ -5406,7 +6304,7 @@
       </c>
       <c r="W77" s="6"/>
     </row>
-    <row r="78" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>151</v>
       </c>
@@ -5438,7 +6336,7 @@
         <v>2999.8049268750005</v>
       </c>
     </row>
-    <row r="79" spans="2:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" t="s">
         <v>147</v>
       </c>
@@ -5473,7 +6371,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>151</v>
       </c>
@@ -5490,7 +6388,7 @@
       </c>
       <c r="G80" s="41"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>147</v>
       </c>
@@ -5510,7 +6408,7 @@
         <v>40000.195073125004</v>
       </c>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>147</v>
       </c>
@@ -5524,7 +6422,7 @@
       </c>
       <c r="G82" s="56"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>151</v>
       </c>
@@ -5541,7 +6439,7 @@
       </c>
       <c r="G83" s="56"/>
     </row>
-    <row r="84" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C84" s="7" t="s">
         <v>89</v>
       </c>
@@ -5552,10 +6450,10 @@
       </c>
       <c r="G84" s="59"/>
     </row>
-    <row r="85" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F85" s="25"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
         <v>116</v>
       </c>
@@ -5566,7 +6464,7 @@
       </c>
       <c r="G86" s="4"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C87" s="5"/>
       <c r="D87" t="s">
         <v>128</v>
@@ -5579,7 +6477,7 @@
       </c>
       <c r="G87" s="6"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C88" s="5"/>
       <c r="D88">
         <v>1</v>
@@ -5594,7 +6492,7 @@
       <c r="G88" s="6"/>
       <c r="J88" s="62"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C89" s="5"/>
       <c r="D89">
         <v>2</v>
@@ -5609,7 +6507,7 @@
       <c r="G89" s="6"/>
       <c r="J89" s="62"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C90" s="5"/>
       <c r="D90">
         <v>3</v>
@@ -5624,7 +6522,7 @@
       <c r="G90" s="6"/>
       <c r="J90" s="62"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C91" s="5"/>
       <c r="D91">
         <v>4</v>
@@ -5638,7 +6536,7 @@
       </c>
       <c r="G91" s="6"/>
     </row>
-    <row r="92" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C92" s="63" t="s">
         <v>131</v>
       </c>
@@ -5652,8 +6550,8 @@
       </c>
       <c r="G92" s="9"/>
     </row>
-    <row r="94" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C95" t="s">
         <v>119</v>
       </c>
@@ -5666,7 +6564,7 @@
       </c>
       <c r="G95" s="21"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C96" s="5"/>
       <c r="D96" t="s">
         <v>128</v>
@@ -5679,7 +6577,7 @@
       </c>
       <c r="G96" s="65"/>
     </row>
-    <row r="97" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C97" s="5"/>
       <c r="D97">
         <v>1</v>
@@ -5693,7 +6591,7 @@
       </c>
       <c r="G97" s="6"/>
     </row>
-    <row r="98" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C98" s="5"/>
       <c r="D98">
         <v>2</v>
@@ -5707,7 +6605,7 @@
       </c>
       <c r="G98" s="6"/>
     </row>
-    <row r="99" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C99" s="5"/>
       <c r="D99">
         <v>3</v>
@@ -5721,7 +6619,7 @@
       </c>
       <c r="G99" s="6"/>
     </row>
-    <row r="100" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C100" s="5"/>
       <c r="D100">
         <v>4</v>
@@ -5735,7 +6633,7 @@
       </c>
       <c r="G100" s="6"/>
     </row>
-    <row r="101" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C101" s="63" t="s">
         <v>131</v>
       </c>
@@ -5749,8 +6647,8 @@
       </c>
       <c r="G101" s="9"/>
     </row>
-    <row r="103" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="104" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>103</v>
       </c>
@@ -5766,7 +6664,7 @@
       </c>
       <c r="H104" s="4"/>
     </row>
-    <row r="105" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C105" s="69" t="s">
         <v>171</v>
       </c>
@@ -5780,7 +6678,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="106" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C106" s="69" t="s">
         <v>173</v>
       </c>
@@ -5792,7 +6690,7 @@
       </c>
       <c r="H106" s="6"/>
     </row>
-    <row r="107" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C107" s="70" t="s">
         <v>176</v>
       </c>
@@ -5801,8 +6699,8 @@
       <c r="G107" s="8"/>
       <c r="H107" s="9"/>
     </row>
-    <row r="108" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="109" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="2:14" x14ac:dyDescent="0.25">
       <c r="I109" s="2" t="s">
         <v>75</v>
       </c>
@@ -5814,7 +6712,7 @@
       <c r="M109" s="3"/>
       <c r="N109" s="4"/>
     </row>
-    <row r="110" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:14" x14ac:dyDescent="0.25">
       <c r="D110">
         <v>1</v>
       </c>
@@ -5838,7 +6736,7 @@
       </c>
       <c r="N110" s="6"/>
     </row>
-    <row r="111" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>178</v>
       </c>
@@ -5857,7 +6755,7 @@
       <c r="I111" s="5"/>
       <c r="N111" s="6"/>
     </row>
-    <row r="112" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C112" s="2" t="s">
         <v>179</v>
       </c>
@@ -5888,7 +6786,7 @@
       </c>
       <c r="N112" s="6"/>
     </row>
-    <row r="113" spans="3:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C113" s="5" t="s">
         <v>180</v>
       </c>
@@ -5925,7 +6823,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="114" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C114" s="7" t="s">
         <v>182</v>
       </c>
@@ -5958,7 +6856,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="115" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E115" s="16" t="s">
         <v>184</v>
       </c>
@@ -5986,4 +6884,775 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7B34B5-690B-4D21-B3B0-0F39CF72B619}">
+  <dimension ref="B24:G42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" t="s">
+        <v>204</v>
+      </c>
+      <c r="D24" s="74">
+        <v>5100000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D25" s="74">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" s="74">
+        <v>227000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>207</v>
+      </c>
+      <c r="D27" s="74">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D28" s="75">
+        <f>SUM(D24:D27)</f>
+        <v>5612000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" t="s">
+        <v>186</v>
+      </c>
+      <c r="D30" s="15">
+        <v>0.24</v>
+      </c>
+      <c r="E30" s="25">
+        <f>D30*E33</f>
+        <v>1346880</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" s="15">
+        <v>0.38</v>
+      </c>
+      <c r="E31" s="25">
+        <f>D31*E33</f>
+        <v>2132560</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>188</v>
+      </c>
+      <c r="D32" s="15">
+        <v>0.38</v>
+      </c>
+      <c r="E32" s="25">
+        <f>D32*E33</f>
+        <v>2132560</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D33" s="76">
+        <f>SUM(D30:D32)</f>
+        <v>1</v>
+      </c>
+      <c r="E33" s="75">
+        <v>5612000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>246</v>
+      </c>
+      <c r="C36" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" t="s">
+        <v>251</v>
+      </c>
+      <c r="E36" t="s">
+        <v>247</v>
+      </c>
+      <c r="F36" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>186</v>
+      </c>
+      <c r="E37">
+        <v>1346880</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>187</v>
+      </c>
+      <c r="E38">
+        <v>2132560</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>188</v>
+      </c>
+      <c r="E39">
+        <v>2132560</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D40" s="79" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40">
+        <v>2525400</v>
+      </c>
+      <c r="G40" s="15">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D41" s="79" t="s">
+        <v>249</v>
+      </c>
+      <c r="F41">
+        <v>3086600</v>
+      </c>
+      <c r="G41" s="15">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D42" s="78" t="s">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{862D46F1-C7F2-4B62-8937-31D72D70B386}">
+  <dimension ref="B26:I44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>203</v>
+      </c>
+      <c r="C26" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>246</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F31" s="16" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C32">
+        <v>2021</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C33">
+        <v>2022</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C34">
+        <v>2023</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C35">
+        <v>2024</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>267</v>
+      </c>
+      <c r="C37" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C39" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F40" s="16" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C41">
+        <v>2021</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C42">
+        <v>2022</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C43">
+        <v>2023</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="C44">
+        <v>2024</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>266</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12591C51-F13F-4D16-B1CA-1C7B32F3D87B}">
+  <dimension ref="C9:F24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="5.140625" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="25">
+        <v>46400</v>
+      </c>
+      <c r="E10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11">
+        <v>6400</v>
+      </c>
+      <c r="E11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="26">
+        <f>D10-D11</f>
+        <v>40000</v>
+      </c>
+      <c r="E12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="27">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" s="25">
+        <v>500000</v>
+      </c>
+      <c r="E14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15">
+        <f>D12/D13</f>
+        <v>10000</v>
+      </c>
+      <c r="E15" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>194</v>
+      </c>
+      <c r="D16" s="72">
+        <f>D12/D14</f>
+        <v>0.08</v>
+      </c>
+      <c r="E16" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" s="34">
+        <v>10000</v>
+      </c>
+      <c r="E20">
+        <f>F20*D$16</f>
+        <v>8800</v>
+      </c>
+      <c r="F20">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D21" s="34">
+        <v>10000</v>
+      </c>
+      <c r="E21">
+        <f t="shared" ref="E21:E23" si="0">F21*D$16</f>
+        <v>9200</v>
+      </c>
+      <c r="F21">
+        <v>115000</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="34">
+        <v>10000</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>10160</v>
+      </c>
+      <c r="F22">
+        <v>127000</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" s="34">
+        <v>10000</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>11840</v>
+      </c>
+      <c r="F23">
+        <v>148000</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="71">
+        <f>SUM(D20:D23)</f>
+        <v>40000</v>
+      </c>
+      <c r="E24">
+        <f>F24*D$16</f>
+        <v>40000</v>
+      </c>
+      <c r="F24">
+        <f>SUM(F20:F23)</f>
+        <v>500000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33ED7D8E-6E0A-4890-B88F-16D13BA12206}">
+  <dimension ref="B19:G26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" t="s">
+        <v>188</v>
+      </c>
+      <c r="D19">
+        <v>50000</v>
+      </c>
+      <c r="G19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>210</v>
+      </c>
+      <c r="D20">
+        <v>1300</v>
+      </c>
+      <c r="G20" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>209</v>
+      </c>
+      <c r="D22">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D23" s="77">
+        <f>SUM(D19:D22)</f>
+        <v>54200</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C25" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F26" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8603A5-ECDA-4924-BA5E-9368E679B896}">
+  <dimension ref="B9:F21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F9" s="16"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" s="74">
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12" s="74">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="74">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D14" s="74">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="75">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>208</v>
+      </c>
+      <c r="C17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="25">
+        <v>1075000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="25">
+        <v>645000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>188</v>
+      </c>
+      <c r="D19" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="E19" s="25">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D20" s="76">
+        <f>SUM(D17:D19)</f>
+        <v>1</v>
+      </c>
+      <c r="E20" s="75">
+        <v>2150000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>